--- a/packages/rc9_2_2_production/inputs/NMG_EN_AND_SP.xlsx
+++ b/packages/rc9_2_2_production/inputs/NMG_EN_AND_SP.xlsx
@@ -1289,25 +1289,25 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="7">
-    <dataValidation sqref="C7 C16 C18 C22 C23 C24 C28 C29 C30 C31 C33 C44 C46" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C7 C16 C18 C22 C23 C24 C28 C29 C30 C31 C33 C44 C46" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted.">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C8" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted.">
       <formula1>"15,30,60"</formula1>
     </dataValidation>
-    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C9" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted.">
       <formula1>"FT Wise 15 Min,FT Wise 30 Min,FT Wise 60 Min"</formula1>
     </dataValidation>
-    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C10" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted.">
       <formula1>"Shrinkage 15 Min,Shrinkage 30 Min,Shrinkage 60 Min"</formula1>
     </dataValidation>
-    <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted.">
       <formula1>"Before Breaks Only,Full Schedule"</formula1>
     </dataValidation>
-    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted.">
       <formula1>"Quick,Deep,Overnight"</formula1>
     </dataValidation>
-    <dataValidation sqref="C49" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C49" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted.">
       <formula1>"Warn,Fail,Off"</formula1>
     </dataValidation>
   </dataValidations>
@@ -7612,13 +7612,13 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C5" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted.">
       <formula1>"Auto,Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="C10 C20 C25 C28 C30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C10 C20 C25 C28 C30" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted.">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation sqref="C18 C23 C27" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C18 C23 C27" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" type="list" errorStyle="stop" errorTitle="Value not allowed" error="Choose a value from the list. Typed values outside the list are not accepted.">
       <formula1>"Warn,Fail,Off"</formula1>
     </dataValidation>
   </dataValidations>
